--- a/system_design/Georgetown/V0.5/bill_of_materials.xlsx
+++ b/system_design/Georgetown/V0.5/bill_of_materials.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\UAV-Deployable-Stage-Height-Sensor\system_design\Georgetown\V0.5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE0C2F53-A9FB-4AC2-A3D1-F6F09FE6B6E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92FC9251-22EE-4CB6-81B0-D0434CABC585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="136">
   <si>
     <t>Arduino Nano</t>
   </si>
@@ -402,9 +402,6 @@
   </si>
   <si>
     <t>https://www.ebay.com/itm/135516167050?_skw=B3B-XH-A&amp;itmmeta=01JXJN27KW3SV3ZA95H65390XD&amp;hash=item1f8d649b8a:g:2rIAAOSwhWlnlDUD&amp;itmprp=enc%3AAQAKAAAAwFkggFvd1GGDu0w3yXCmi1cVMih7yC%2FWve52RdwhMAlOgWsL1OoLM4xoBnc%2B7VbJxO7%2Fl5Q2%2B19FN%2Ffcf4Nh7uGxttthvmZ%2BZODMfmWlr3tqV99qA67ltarFMPt0GZ5Q0hGKwVEs3cWQzRsgzIEMfPrKwt%2FXoqS0kqv8N3acTaphgw--%2B1HloQZc3MjBQEeC3t1OszQttaoyVtLG7P0WoB7S3sUOfGn60RdftLEZV%2BMqhhcdr8JYIK2PYQMDH3SJaA%3D%3D%7Ctkp%3ABk9SR5b6iNXsZQ</t>
-  </si>
-  <si>
-    <t>4 inch</t>
   </si>
   <si>
     <t>https://www.staples.com/centon-micro-8gb-sdhc-memory-card-uhs1-5-pack-s1-msdhu1-8g-5-b/product_24298979?locupd=y</t>
@@ -903,13 +900,13 @@
         <v>88</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -926,6 +923,7 @@
         <v>25.7</v>
       </c>
       <c r="E2" s="4">
+        <f>C2*D2</f>
         <v>25.7</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -952,6 +950,7 @@
         <v>2.52</v>
       </c>
       <c r="E3" s="4">
+        <f t="shared" ref="E3:E33" si="0">C3*D3</f>
         <v>2.52</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -975,6 +974,7 @@
         <v>1.4</v>
       </c>
       <c r="E4" s="4">
+        <f t="shared" si="0"/>
         <v>1.4</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -1001,6 +1001,7 @@
         <v>11.96</v>
       </c>
       <c r="E5" s="4">
+        <f t="shared" si="0"/>
         <v>11.96</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -1024,6 +1025,7 @@
         <v>5.26</v>
       </c>
       <c r="E6" s="4">
+        <f t="shared" si="0"/>
         <v>5.26</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -1050,6 +1052,7 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="E7" s="4">
+        <f t="shared" si="0"/>
         <v>2.0299999999999998</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -1076,6 +1079,7 @@
         <v>15.2</v>
       </c>
       <c r="E8" s="4">
+        <f t="shared" si="0"/>
         <v>15.2</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -1096,6 +1100,7 @@
         <v>5.25</v>
       </c>
       <c r="E9" s="4">
+        <f t="shared" si="0"/>
         <v>5.25</v>
       </c>
       <c r="F9" s="1" t="s">
@@ -1122,6 +1127,7 @@
         <v>18</v>
       </c>
       <c r="E10" s="4">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -1148,6 +1154,7 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="E11" s="4">
+        <f t="shared" si="0"/>
         <v>1.0900000000000001</v>
       </c>
       <c r="F11" s="1" t="s">
@@ -1171,6 +1178,7 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="E12" s="4">
+        <f t="shared" si="0"/>
         <v>0.57999999999999996</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -1194,6 +1202,7 @@
         <v>8.23</v>
       </c>
       <c r="E13" s="4">
+        <f t="shared" si="0"/>
         <v>8.23</v>
       </c>
       <c r="F13" s="1" t="s">
@@ -1214,25 +1223,26 @@
         <v>8.24</v>
       </c>
       <c r="E14" s="4">
+        <f t="shared" si="0"/>
         <v>8.24</v>
       </c>
       <c r="F14" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>105</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1249,6 +1259,7 @@
         <v>2.0299999999999998</v>
       </c>
       <c r="E15" s="4">
+        <f t="shared" si="0"/>
         <v>2.0299999999999998</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -1272,6 +1283,7 @@
         <v>0.2</v>
       </c>
       <c r="E16" s="4">
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
       <c r="F16" s="1" t="s">
@@ -1295,7 +1307,8 @@
         <v>0.1</v>
       </c>
       <c r="E17" s="4">
-        <v>0.7</v>
+        <f t="shared" si="0"/>
+        <v>0.70000000000000007</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>86</v>
@@ -1318,7 +1331,8 @@
         <v>0.1</v>
       </c>
       <c r="E18" s="4">
-        <v>0.7</v>
+        <f t="shared" si="0"/>
+        <v>0.70000000000000007</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>85</v>
@@ -1341,7 +1355,8 @@
         <v>0.1</v>
       </c>
       <c r="E19" s="4">
-        <v>0.7</v>
+        <f t="shared" si="0"/>
+        <v>0.70000000000000007</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>84</v>
@@ -1364,6 +1379,7 @@
         <v>0.34</v>
       </c>
       <c r="E20" s="4">
+        <f t="shared" si="0"/>
         <v>0.34</v>
       </c>
       <c r="F20" s="1" t="s">
@@ -1387,6 +1403,7 @@
         <v>0.39</v>
       </c>
       <c r="E21" s="4">
+        <f t="shared" si="0"/>
         <v>0.39</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -1410,6 +1427,7 @@
         <v>0.41</v>
       </c>
       <c r="E22" s="4">
+        <f t="shared" si="0"/>
         <v>0.41</v>
       </c>
       <c r="F22" s="1" t="s">
@@ -1433,6 +1451,7 @@
         <v>0.26</v>
       </c>
       <c r="E23" s="4">
+        <f t="shared" si="0"/>
         <v>0.26</v>
       </c>
       <c r="F23" s="1" t="s">
@@ -1456,6 +1475,7 @@
         <v>0.48</v>
       </c>
       <c r="E24" s="4">
+        <f t="shared" si="0"/>
         <v>1.92</v>
       </c>
       <c r="F24" s="1" t="s">
@@ -1479,6 +1499,7 @@
         <v>3.58</v>
       </c>
       <c r="E25" s="4">
+        <f t="shared" si="0"/>
         <v>3.58</v>
       </c>
       <c r="F25" s="1" t="s">
@@ -1498,14 +1519,15 @@
       <c r="B26" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>122</v>
+      <c r="C26" s="2">
+        <v>1</v>
       </c>
       <c r="D26" s="4">
-        <v>2.9</v>
+        <v>60.76</v>
       </c>
       <c r="E26" s="4">
-        <v>2.9</v>
+        <f t="shared" si="0"/>
+        <v>60.76</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>118</v>
@@ -1525,6 +1547,7 @@
         <v>0.91</v>
       </c>
       <c r="E27" s="4">
+        <f t="shared" si="0"/>
         <v>0.91</v>
       </c>
       <c r="F27" s="1" t="s">
@@ -1548,6 +1571,7 @@
         <v>2.15</v>
       </c>
       <c r="E28" s="4">
+        <f t="shared" si="0"/>
         <v>2.15</v>
       </c>
       <c r="F28" s="1" t="s">
@@ -1571,6 +1595,7 @@
         <v>0.13</v>
       </c>
       <c r="E29" s="4">
+        <f t="shared" si="0"/>
         <v>0.13</v>
       </c>
       <c r="F29" s="1" t="s">
@@ -1594,7 +1619,8 @@
         <v>7.39</v>
       </c>
       <c r="E30" s="4">
-        <v>66.510000000000005</v>
+        <f t="shared" si="0"/>
+        <v>66.509999999999991</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>70</v>
@@ -1602,7 +1628,7 @@
     </row>
     <row r="31" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C31" s="2">
         <v>2</v>
@@ -1611,13 +1637,14 @@
         <v>0.01</v>
       </c>
       <c r="E31" s="4">
+        <f t="shared" si="0"/>
         <v>0.02</v>
       </c>
       <c r="F31" s="1"/>
     </row>
     <row r="32" spans="1:8" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C32" s="2">
         <v>2</v>
@@ -1626,18 +1653,19 @@
         <v>7.2999999999999995E-2</v>
       </c>
       <c r="E32" s="4">
-        <v>0.14000000000000001</v>
+        <f t="shared" si="0"/>
+        <v>0.14599999999999999</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:6" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C33" s="2">
         <v>1</v>
@@ -1646,10 +1674,11 @@
         <v>4.7</v>
       </c>
       <c r="E33" s="4">
+        <f t="shared" si="0"/>
         <v>4.7</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1658,7 +1687,7 @@
       </c>
       <c r="E34" s="5">
         <f>SUM(E2:E33)</f>
-        <v>194.15</v>
+        <v>252.01599999999999</v>
       </c>
     </row>
   </sheetData>
